--- a/templates/KTS-Weekstaat-template-RevA.xlsx
+++ b/templates/KTS-Weekstaat-template-RevA.xlsx
@@ -29,7 +29,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="0007567F"/>
-      <sz val="24"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -67,14 +67,14 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="000F1B2D"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F1B2D"/>
-      <sz val="20"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -192,12 +192,14 @@
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -206,46 +208,46 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -326,12 +328,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>7</col>
+      <col>0</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="695325"/>
+    <ext cx="209550" cy="209550"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -339,6 +341,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="857250" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -641,136 +668,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>URENSTAAT</t>
+          <t xml:space="preserve">  URENSTAAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NAAM</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PERIODE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>NAAM</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>PERIODE</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>[Vul je naam in]</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Week XX · 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Nieuwboerweg 2A, 1738BB Waarland</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>[Vul je naam in]</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Week XX - 2026</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>+31 6 5123 9050  -  info@kuijpers-ts.nl</t>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>OPDRACHTGEVER</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+31 6 5123 9050  ·  info@kuijpers-ts.nl</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>PROJECT</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>OPDRACHTGEVER</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>[Projectnaam]</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>[Klantnaam]</t>
         </is>
       </c>
     </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>DAG</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>DATUM</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>BEGINTIJD</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>EINDTIJD</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>PAUZE</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>GEW. UREN</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>WERKZAAMHEDEN</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>LOCATIE</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>KM</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>DAG</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>DATUM</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>BEGINTIJD</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>EINDTIJD</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>PAUZE</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>GEW. UREN</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>WERKZAAMHEDEN</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>LOCATIE</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>KM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Maandag</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="8" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="9" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Maandag</t>
+          <t>Dinsdag</t>
         </is>
       </c>
       <c r="B11" s="9" t="n"/>
@@ -778,14 +822,14 @@
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
-      <c r="G11" s="10" t="n"/>
-      <c r="H11" s="10" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
       <c r="I11" s="9" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Dinsdag</t>
+          <t>Woensdag</t>
         </is>
       </c>
       <c r="B12" s="9" t="n"/>
@@ -793,14 +837,14 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
       <c r="F12" s="9" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
+      <c r="G12" s="8" t="n"/>
+      <c r="H12" s="8" t="n"/>
       <c r="I12" s="9" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Woensdag</t>
+          <t>Donderdag</t>
         </is>
       </c>
       <c r="B13" s="9" t="n"/>
@@ -808,14 +852,14 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="G13" s="8" t="n"/>
+      <c r="H13" s="8" t="n"/>
       <c r="I13" s="9" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Donderdag</t>
+          <t>Vrijdag</t>
         </is>
       </c>
       <c r="B14" s="9" t="n"/>
@@ -823,186 +867,175 @@
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
       <c r="F14" s="9" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="10" t="n"/>
+      <c r="G14" s="8" t="n"/>
+      <c r="H14" s="8" t="n"/>
       <c r="I14" s="9" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Vrijdag</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Zaterdag</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n"/>
-      <c r="I15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Zaterdag</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="I15" s="11" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Zondag</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="13" t="n"/>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="12" t="n"/>
-    </row>
-    <row r="19" ht="14" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="11" t="n"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>REGULIER MA-VR</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>ZATERDAG</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>ZONDAG/FEEST</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>REIS KM</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>TOTAAL TE FACTUREREN</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>OPMERKINGEN</t>
         </is>
       </c>
-      <c r="H19" s="17" t="n"/>
-      <c r="I19" s="18" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="19">
-        <f>SUM(F11:F15)</f>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="16">
+        <f>SUM(F10:F14)</f>
         <v/>
       </c>
-      <c r="B20" s="19">
+      <c r="B19" s="16">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="C19" s="16">
         <f>F16</f>
         <v/>
       </c>
-      <c r="C20" s="19">
-        <f>F17</f>
+      <c r="D19" s="16">
+        <f>SUM(I10:I16)</f>
         <v/>
       </c>
-      <c r="D20" s="19">
-        <f>SUM(I11:I17)</f>
+      <c r="E19" s="17">
+        <f>SUM(F10:F16)</f>
         <v/>
       </c>
-      <c r="E20" s="20">
-        <f>SUM(F11:F17)</f>
-        <v/>
-      </c>
-      <c r="G20" s="21" t="n"/>
-      <c r="H20" s="17" t="n"/>
-      <c r="I20" s="18" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="20" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>HANDTEKENING OPDRACHTNEMER</t>
         </is>
       </c>
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="23" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="23" t="n"/>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="B21" s="22" t="n"/>
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>HANDTEKENING OPDRACHTGEVER</t>
         </is>
       </c>
-      <c r="G22" s="23" t="n"/>
-      <c r="H22" s="23" t="n"/>
-      <c r="I22" s="23" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="23" t="n"/>
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="23" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
-      <c r="F23" s="23" t="n"/>
-      <c r="G23" s="23" t="n"/>
-      <c r="H23" s="23" t="n"/>
-      <c r="I23" s="23" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="23" t="n"/>
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="23" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
-      <c r="F24" s="23" t="n"/>
-      <c r="G24" s="23" t="n"/>
-      <c r="H24" s="23" t="n"/>
-      <c r="I24" s="23" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="23" t="n"/>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="23" t="n"/>
-      <c r="H25" s="23" t="n"/>
-      <c r="I25" s="23" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="22" t="n"/>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="22" t="n"/>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="22" t="n"/>
+      <c r="B24" s="22" t="n"/>
+      <c r="C24" s="22" t="n"/>
+      <c r="D24" s="22" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>Op deze opdracht zijn de Algemene Voorwaarden Detachering 2026 van Kuijpers Technical Services BV van toepassing.</t>
         </is>
       </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>KvK 93410557  ·  BTW NL866385368B01</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="F4:I4"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="G20:I20"/>
+  <mergeCells count="12">
+    <mergeCell ref="F18:I18"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F19:I19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="F5:I5"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="H26:I26"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/templates/KTS-Weekstaat-template-RevA.xlsx
+++ b/templates/KTS-Weekstaat-template-RevA.xlsx
@@ -685,7 +685,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  URENSTAAT</t>
+          <t xml:space="preserve">  WEEKSTAAT</t>
         </is>
       </c>
     </row>
